--- a/dataset_t6_grouped/results2/G2/G2_T1448_W0038F0002T0006Z000C1N24_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T1448_W0038F0002T0006Z000C1N24_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>40.52704026694197</v>
+        <v>6.585644043378071</v>
       </c>
       <c r="D2" t="n">
-        <v>40.4489444484718</v>
+        <v>6.572953472876668</v>
       </c>
       <c r="E2" t="n">
-        <v>11.64360330183024</v>
+        <v>1.892085536547414</v>
       </c>
       <c r="F2" t="n">
-        <v>8.572810273485731</v>
+        <v>1.393081669441431</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>40.45456751754758</v>
+        <v>6.573867221601482</v>
       </c>
       <c r="D3" t="n">
-        <v>38.28172307425324</v>
+        <v>6.220779999566151</v>
       </c>
       <c r="E3" t="n">
-        <v>11.64360330183024</v>
+        <v>1.892085536547414</v>
       </c>
       <c r="F3" t="n">
-        <v>8.572810273485731</v>
+        <v>1.393081669441431</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>15.82425256052484</v>
+        <v>2.571441041085286</v>
       </c>
       <c r="D4" t="n">
-        <v>25.88849957177762</v>
+        <v>4.206881180413863</v>
       </c>
       <c r="E4" t="n">
-        <v>11.64360330183024</v>
+        <v>1.892085536547414</v>
       </c>
       <c r="F4" t="n">
-        <v>8.572810273485731</v>
+        <v>1.393081669441431</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>13.24929793892585</v>
+        <v>2.153010915075451</v>
       </c>
       <c r="D5" t="n">
-        <v>17.59717853420434</v>
+        <v>2.859541511808205</v>
       </c>
       <c r="E5" t="n">
-        <v>11.64360330183024</v>
+        <v>1.892085536547414</v>
       </c>
       <c r="F5" t="n">
-        <v>8.572810273485731</v>
+        <v>1.393081669441431</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>26.43093185070728</v>
+        <v>4.295026425739933</v>
       </c>
       <c r="D6" t="n">
-        <v>25.53018930646374</v>
+        <v>4.148655762300358</v>
       </c>
       <c r="E6" t="n">
-        <v>11.64360330183024</v>
+        <v>1.892085536547414</v>
       </c>
       <c r="F6" t="n">
-        <v>8.572810273485731</v>
+        <v>1.393081669441431</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
